--- a/data/재고_입력_양식.xlsx
+++ b/data/재고_입력_양식.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="재고입력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재고입력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>카테고리</t>
+          <t>공정코드</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -7770,8 +7770,8 @@
     <mergeCell ref="A5:L5"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="B6:B505" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="카테고리 값은 드롭다운 목록에서만 선택 가능합니다.&#10;가능값: RM, TA, HA, VA, BA, FG, UK" promptTitle="카테고리" prompt="드롭다운에서 선택: RM, TA, HA, VA, BA, FG, UK" type="list">
-      <formula1>"RM,TA,HA,VA,BA,FG,UK"</formula1>
+    <dataValidation sqref="B6:B505" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="공정코드 값은 드롭다운 목록에서만 선택 가능합니다.&#10;가능값: TR, TA, TF, HR, HA, HF, VR, VA, VF, NR, NA, NF, AR, AA, AF, PR, PA, PF" promptTitle="공정코드" prompt="드롭다운에서 선택: TR, TA, TF, HR, HA, HF, VR, VA, VF, NR, NA, NF, AR, AA, AF, PR, PA, PF" type="list">
+      <formula1>"TR,TA,TF,HR,HA,HF,VR,VA,VF,NR,NA,NF,AR,AA,AF,PR,PA,PF"</formula1>
     </dataValidation>
     <dataValidation sqref="E6:E505" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="단위 값은 드롭다운 목록에서만 선택 가능합니다.&#10;가능값: EA, SET, kg, g, m, mm, L, box" promptTitle="단위" prompt="드롭다운에서 선택: EA, SET, kg, g, m, mm, L, box" type="list">
       <formula1>"EA,SET,kg,g,m,mm,L,box"</formula1>
@@ -7799,7 +7799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>빨강 칸 3개(품목명/카테고리/현재수량)만 채워도 등록 가능</t>
+          <t>빨강 칸 3개(품목명/공정코드/현재수량)만 채워도 등록 가능</t>
         </is>
       </c>
     </row>
@@ -7871,400 +7871,412 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2. 카테고리 (드롭다운)</t>
+          <t>2. 공정코드 (드롭다운, 18종)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>형식</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>원자재 - 전극, 필라멘트, 게터 등 가공 전 단계 부품</t>
+          <t>{부서 계열 1글자}{단계 1글자}. 부서 6종 × 단계 3종 = 18개</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>단계</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>튜브 어셈블리 - 튜브 조립 단계 반제품</t>
+          <t>R = 원자재 / A = 중간공정(반제품) / F = 공정완료(완제품)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>T_ 튜브</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>고압 어셈블리 - 고압부 조립 단계 반제품</t>
+          <t>TR · TA · TF — 튜브 파트 (원자재 / 중간 / 완료)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>H_ 고압</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>진공 어셈블리 - 진공부 조립 단계 반제품</t>
+          <t>HR · HA · HF — 고압 파트</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>V_ 진공</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>조립 완성 - 고압+진공+튜닝 최종 조립 단계</t>
+          <t>VR · VA · VF — 진공 파트</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>N_ 튜닝</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>완제품 - 출하 준비 끝난 최종 제품</t>
+          <t>NR · NA · NF — 튜닝 파트</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>A_ 조립</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>미분류 - 분류 애매하면 UK 선택, 나중에 관리자가 재분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+          <t>AR · AA · AF — 조립 파트</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>P_ 출하</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>PR · PA · PF — 출하 파트 (PA=가방 포장, PF=박스 포장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3. 모델 (드롭다운)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>공용</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>특정 모델 제품에 묶이지 않는 공용 부품 (디폴트)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>DX3000</t>
+          <t>공용</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>DX3000 시리즈 전용</t>
+          <t>특정 모델 제품에 묶이지 않는 공용 부품 (디폴트)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>ADX4000W</t>
+          <t>DX3000</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>ADX4000W 전용</t>
+          <t>DX3000 시리즈 전용</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ADX6000</t>
+          <t>ADX4000W</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>ADX6000 전용</t>
+          <t>ADX4000W 전용</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>COCOON</t>
+          <t>ADX6000</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>COCOON 시리즈 전용</t>
+          <t>ADX6000 전용</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
+          <t>COCOON</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>COCOON 시리즈 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
           <t>SOLO</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>SOLO 시리즈 전용</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>4. 부서 (드롭다운)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>조립</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>조립 파트</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>고압</t>
+          <t>조립</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>고압 파트</t>
+          <t>조립 파트</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>진공</t>
+          <t>고압</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>진공 파트</t>
+          <t>고압 파트</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>튜닝</t>
+          <t>진공</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>튜닝 파트</t>
+          <t>진공 파트</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>튜브</t>
+          <t>튜닝</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>튜브 파트</t>
+          <t>튜닝 파트</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>튜브</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>AS 파트</t>
+          <t>튜브 파트</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>출하</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>출하/검사 파트</t>
+          <t>AS 파트</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
+          <t>출하</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>출하/검사 파트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>부서 애매하면 '기타' 선택</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>5. 수량 관련</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>현재수량</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>지금 창고에 있는 실물 수량. 0도 괜찮음. 비우면 0 처리.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
+          <t>현재수량</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>지금 창고에 있는 실물 수량. 0도 괜찮음. 비우면 0 처리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
           <t>안전재고</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>이 수량 이하로 떨어지면 경고가 뜰 기준선. 몰라도 됨.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>6. 다 쓴 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>엑셀 저장 (파일명 그대로 두거나 날짜 붙여 저장)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>전달</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Claude에게 "이 양식으로 재고 교체해줘" 라고 말하기</t>
+          <t>엑셀 저장 (파일명 그대로 두거나 날짜 붙여 저장)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>전달</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Claude가 먼저 --dry-run으로 몇 건이 추가/변경될지 보여줌</t>
+          <t>Claude에게 "이 양식으로 재고 교체해줘" 라고 말하기</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Claude가 먼저 --dry-run으로 몇 건이 추가/변경될지 보여줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
           <t>확정</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>"진짜 이걸로 교체" 확인하면 기존 테스트 데이터 삭제 후 반영</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>7. 색깔 뜻</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>반드시 채워야 하는 칸 (비면 그 행은 등록 안 됨)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>알면 채우는 게 좋지만 비워도 등록은 됨</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>있으면 쓰고 없으면 비우기 (품번/바코드 비우면 자동 부여)</t>
         </is>
@@ -8272,14 +8284,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
